--- a/artfynd/A 61164-2024 artfynd.xlsx
+++ b/artfynd/A 61164-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>56218784</v>
       </c>
       <c r="B2" t="n">
-        <v>89832</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536510.4099079657</v>
+        <v>536510</v>
       </c>
       <c r="R2" t="n">
-        <v>7043057.188286403</v>
+        <v>7043057</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2013-11-05</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2013-11-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,37 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56218776</v>
+        <v>56218783</v>
       </c>
       <c r="B3" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536556.5846145926</v>
+        <v>536524</v>
       </c>
       <c r="R3" t="n">
-        <v>7043123.790480646</v>
+        <v>7043084</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,27 +844,18 @@
           <t>2013-11-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-11-05</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,37 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56218783</v>
+        <v>56218776</v>
       </c>
       <c r="B4" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>536523.9591837432</v>
+        <v>536557</v>
       </c>
       <c r="R4" t="n">
-        <v>7043084.129965332</v>
+        <v>7043124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,28 +946,17 @@
           <t>2013-11-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2013-11-05</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1027,16 +982,11 @@
         <v>56218775</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1064,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>536528.219354999</v>
+        <v>536528</v>
       </c>
       <c r="R5" t="n">
-        <v>7042985.514694107</v>
+        <v>7042986</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,19 +1047,9 @@
           <t>2013-11-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-11-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,122 +1073,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>56218782</v>
-      </c>
-      <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Söder om Recksjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>536496.786480136</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7043192.747272929</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2013-11-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2013-11-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Sebastian Acker</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>

--- a/artfynd/A 61164-2024 artfynd.xlsx
+++ b/artfynd/A 61164-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218784</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218783</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218776</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,8 +1097,19 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56218775</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>